--- a/data/trans_orig/IP07KS_C02_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C02_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse lleno/a de energía en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de sentirse lleno/a de energía, percibida por el/la menor [KIDSCREEN 10] en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12381</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>54,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>73,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7521</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4440</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10228</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>60,62%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,79%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9058</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16579</t>
+          <t>17614</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>12890</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>22371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,84%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4353</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8325</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3988</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7116</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32,14%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>57,36%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>13278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>43,23%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,11%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>898</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4473</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>27,9%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3425</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>511</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4622</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4492</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4487</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>26,81%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1856</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1856</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5563</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6053</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>33,21%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5550</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>124962</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>109362</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>140983</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>62,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>54,59%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>107088</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>92936</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>129839</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>67,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>58,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>81,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>127669</t>
+          <t>87867</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110665</t>
+          <t>77572</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143049</t>
+          <t>97518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>234757</t>
+          <t>212830</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>211760</t>
+          <t>195736</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264798</t>
+          <t>231535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44927</t>
+          <t>60046</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25818</t>
+          <t>45402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57847</t>
+          <t>75252</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58454</t>
+          <t>46990</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44006</t>
+          <t>37414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74740</t>
+          <t>56175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>103381</t>
+          <t>107036</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78849</t>
+          <t>91298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123958</t>
+          <t>124676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13075</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6294</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28080</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6029</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2505</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12372</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36288</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20128</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>34897</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -1741,107 +1741,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4083</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5652</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4348</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5779</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29645</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23448</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>36003</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56,99%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>69,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>21965</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16809</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>26839</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>56,68%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>43,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29645</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23405</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35800</t>
+          <t>28740</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>51610</t>
+          <t>52647</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43055</t>
+          <t>43549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58947</t>
+          <t>60958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,56%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20255</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14244</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>26741</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,94%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>27,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>51,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>13167</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>8921</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18770</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>33,98%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>48,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25738</t>
+          <t>19440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>32867</t>
+          <t>34122</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25606</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41284</t>
+          <t>42949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5071</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3457</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1392</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7656</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>52014</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>52014</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>52014</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51457</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51457</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51457</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>90209</t>
+          <t>92983</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>90209</t>
+          <t>92983</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>90209</t>
+          <t>92983</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>163711</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>146448</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>181516</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>60,83%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>54,42%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>67,45%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>136574</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>119750</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>165248</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>56,9%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>78,51%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>166372</t>
+          <t>119379</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148053</t>
+          <t>106870</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>185299</t>
+          <t>131838</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>302946</t>
+          <t>283091</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>281090</t>
+          <t>261038</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>336945</t>
+          <t>302017</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>84654</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>68859</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>101604</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>31,46%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>25,59%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>37,76%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>62081</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>37962</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>76506</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>36,35%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>82684</t>
+          <t>64968</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>53831</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>99353</t>
+          <t>77034</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>144765</t>
+          <t>149622</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>117545</t>
+          <t>130502</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>168680</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>14606</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>7833</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>28714</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>10384</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>5591</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>17239</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37399</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>17546</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42008</t>
+          <t>42332</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3032</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3031</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8450</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -3218,107 +3218,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>7775</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4664</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4759</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>885</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>8008</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>4449</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>10053</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>4456</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1736</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>269110</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>269110</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>269110</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>270912</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>270912</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>270912</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>481384</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>481384</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>481384</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
